--- a/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
+++ b/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
+++ b/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>16.12.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina ze stwardnieniem guzkowym. Ocena zaawansowania przed rozpoczęciem leczenia.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 95 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyjne po stronie prawej grup: - 2B średnicy 9 mm SUV max 6,1 - 4 wielkości do 18x17x16 mm SUV max do 10,2 - 5 B wielkości do 11 mm SUV max do 5,6 Aktywne metabolicznie węzły chłonne szyjne po stronie lewej grup: - 2A średnicy 9 mm SUVmax 5,7 - 4 średnicy do 9 mm SUV max do 6,3. - 5 B wielkości do 15x11 mm SUV max do 5,0.  Aktywne metabolicznie obszary w topografii mięśnia MOS po stronie prawej wielkości do 10x22 mm wg PET SUV max do 7,0 [Im fuz. 83].  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 8 mm SUV max do 4,2 - przytchawiczy górny lewy wielkości 10 mm SUV max 4,3 - zamostkowe/ w śródpiersiu przednim  po stronie prawej wielkości do 16x11 mm SUV max do 4,1 - lewobocznie od łuku aorty wielkości do 15x24 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Zwłóknienia w nadprzeponowych partiach płuc.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii/ w przyleganiu do ogona trzustki wielkości 14x13x14 mm wg PET SUV max 6,0- zmiana ogniskowa w ogonie trzustki? pakiet węzłowy przy ogonie trzustki?- do weryfikacji w badaniu MR. Rozlanie wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii. Rozlane pogrubienie ściany pęcherza moczowego.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- do łącznej interpretacji z podanym leczeniem i wynikami trepanobiopsji. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym. Stan po endoprotezoplastyce lewego stawu biodrowego.  Wartości referencyjne: MBPS SUVmax 2,0 Prawy płat wątroby SUVmax do 3,0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych szyi, śródpiersia i klatki piersiowej oraz mięśnia MOS prawego. Aktywny metabolicznie obszar w topografii/ w przyleganiu do ogona trzustki - zmiana ogniskowa w ogonie trzustki? pakiet węzłowy przy ogonie trzustki?- do weryfikacji w badaniu MR. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>10.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>01.03.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina ze stwardnieniem guzkowym. Wczesna ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału II obustronnie wielkości do 14mm, SUV max do 2,5. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Wydatniejsze zmiany włókniste w nadprzeponowych segmentach obu płuc. W obu dołach pachowych liczne drobne węzły chłonne oraz pojedyncze wydatniejsze, wielkości do 19x10mm po stronie prawej oraz do 24x16mm po stronie lewej.  Brzuch i miednica: Mierne pobudzenie metaboliczne śledziony, SUV max do 3,1 Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Rozlane pogrubienie ściany pęcherza moczowego, ale pęcherz słabo wypełniony - do kontroli w USG. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.  Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>14.07.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina ze stwardnieniem guzkowym. Wczesna ocena odpowiedzi po 6 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 95mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne podskórne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. W obu dołach pachowych dość liczne drobne i pojedyncze wydatniejsze węzły chłonne.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek. Pogrubienie ściany, zwłaszcza przedniej pęcherza moczowego.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.  Wartości referencyjne: MBPS SUVmax 2,4; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.8</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
+++ b/pacjenci/KRZYSZTOF JERZYKOWSKI.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 95 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne szyjne po stronie prawej grup: - 2B średnicy 9 mm SUV max 6,1 - 4 wielkości do 18x17x16 mm SUV max do 10,2 - 5 B wielkości do 11 mm SUV max do 5,6 Aktywne metabolicznie węzły chłonne szyjne po stronie lewej grup: - 2A średnicy 9 mm SUVmax 5,7 - 4 średnicy do 9 mm SUV max do 6,3. - 5 B wielkości do 15x11 mm SUV max do 5,0.  Aktywne metabolicznie obszary w topografii mięśnia MOS po stronie prawej wielkości do 10x22 mm wg PET SUV max do 7,0 [Im fuz. 83].  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 8 mm SUV max do 4,2 - przytchawiczy górny lewy wielkości 10 mm SUV max 4,3 - zamostkowe/ w śródpiersiu przednim  po stronie prawej wielkości do 16x11 mm SUV max do 4,1 - lewobocznie od łuku aorty wielkości do 15x24 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Zwłóknienia w nadprzeponowych partiach płuc.  Brzuch i miednica: Aktywny metabolicznie obszar w topografii/ w przyleganiu do ogona trzustki wielkości 14x13x14 mm wg PET SUV max 6,0- zmiana ogniskowa w ogonie trzustki? pakiet węzłowy przy ogonie trzustki?- do weryfikacji w badaniu MR. Rozlanie wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii. Rozlane pogrubienie ściany pęcherza moczowego.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- do łącznej interpretacji z podanym leczeniem i wynikami trepanobiopsji. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym. Stan po endoprotezoplastyce lewego stawu biodrowego.  Wartości referencyjne: MBPS SUVmax 2,0 Prawy płat wątroby SUVmax do 3,0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne szyjne po stronie prawej grup: - 2B średnicy 9 mm SUV max 6,1 - 4 wielkości do 18x17x16 mm SUV max do 10,2 - 5 B wielkości do 11 mm SUV max do 5,6 Aktywne metabolicznie węzły chłonne szyjne po stronie lewej grup: - 2A średnicy 9 mm SUVmax 5,7 - 4 średnicy do 9 mm SUV max do 6,3. - 5 B wielkości do 15x11 mm SUV max do 5,0.  Aktywne metabolicznie obszary w topografii mięśnia MOS po stronie prawej wielkości do 10x22 mm wg PET SUV max do 7,0 [Im fuz. 83].  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 8 mm SUV max do 4,2 - przytchawiczy górny lewy wielkości 10 mm SUV max 4,3 - zamostkowe/ w śródpiersiu przednim  po stronie prawej wielkości do 16x11 mm SUV max do 4,1 - lewobocznie od łuku aorty wielkości do 15x24 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Zwłóknienia w nadprzeponowych partiach płuc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w topografii/ w przyleganiu do ogona trzustki wielkości 14x13x14 mm wg PET SUV max 6,0- zmiana ogniskowa w ogonie trzustki? pakiet węzłowy przy ogonie trzustki?- do weryfikacji w badaniu MR. Rozlanie wzmożony metabolizm FDG w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii. Rozlane pogrubienie ściany pęcherza moczowego.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- do łącznej interpretacji z podanym leczeniem i wynikami trepanobiopsji. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym. Stan po endoprotezoplastyce lewego stawu biodrowego.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem węzłów chłonnych szyi, śródpiersia i klatki piersiowej oraz mięśnia MOS prawego. Aktywny metabolicznie obszar w topografii/ w przyleganiu do ogona trzustki - zmiana ogniskowa w ogonie trzustki? pakiet węzłowy przy ogonie trzustki?- do weryfikacji w badaniu MR. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału II obustronnie wielkości do 14mm, SUV max do 2,5. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Wydatniejsze zmiany włókniste w nadprzeponowych segmentach obu płuc. W obu dołach pachowych liczne drobne węzły chłonne oraz pojedyncze wydatniejsze, wielkości do 19x10mm po stronie prawej oraz do 24x16mm po stronie lewej.  Brzuch i miednica: Mierne pobudzenie metaboliczne śledziony, SUV max do 3,1 Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Rozlane pogrubienie ściany pęcherza moczowego, ale pęcherz słabo wypełniony - do kontroli w USG. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.  Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne przedziału II obustronnie wielkości do 14mm, SUV max do 2,5. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Wydatniejsze zmiany włókniste w nadprzeponowych segmentach obu płuc. W obu dołach pachowych liczne drobne węzły chłonne oraz pojedyncze wydatniejsze, wielkości do 19x10mm po stronie prawej oraz do 24x16mm po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mierne pobudzenie metaboliczne śledziony, SUV max do 3,1 Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Rozlane pogrubienie ściany pęcherza moczowego, ale pęcherz słabo wypełniony - do kontroli w USG. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem- związane ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 95mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne podskórne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. W obu dołach pachowych dość liczne drobne i pojedyncze wydatniejsze węzły chłonne.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek. Pogrubienie ściany, zwłaszcza przedniej pęcherza moczowego.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.  Wartości referencyjne: MBPS SUVmax 2,4; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Komory boczne mózgu miernie poszerzone - niewielki zanik podkorowy mózgu. Aplazja lewej zatoki czołowej, hypoplazja prawej. Niewielkie zmiany zapalne w sitowiu obustronnie oraz u podstawy obu zatok czołowych, zwłaszcza prawej. Niewielkie lewowypukłe skrzywienie przegrody nosowej, z niewielką ostrogą kostna skierowaną na stronę lewą. Niewielkie przyścienne zgrubienia błony śluzowej w prawej zatoce szczękowej. Miernie powiększony prawy płat tarczycy - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne podskórne zwapnienie w powłokach górnej części KLP po stronie lewej średnicy 5 mm. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate zmiany włókniste obustronnie nadprzeponowo. W obu dołach pachowych dość liczne drobne i pojedyncze wydatniejsze węzły chłonne.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne  w jelitach- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe. Bardzo drobne uwapnione konkrementy w UKM-ach obu nerek. Pogrubienie ściany, zwłaszcza przedniej pęcherza moczowego.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Lewowypukła skolioza kręgosłupa lędźwiowego oraz nieznaczna prawowypukła w odcinku piersiowym. Cechy niestabilności oraz wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym kręgosłupa. Wydatne osteofity na krawędziach tylnych trzonów kręgowych oraz odcinkowe zwapnienia w więzadle podłużnym tylnym w odcinku szyjnym kręgosłupa Wielopoziomowo dyskopatie w odcinku piersiowym i lędźwiowym kręgosłupa. Włamanie grzbietowej części blaszki granicznej dolnej trzonu L3 lub pojedynczy guzek Schmorla wypełniony gazem. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Prawie poziome ułożenie kości krzyżowej. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, ze sklerotyzacją przystawowych struktur kostnych oraz z mostami kostnymi na przednich krawędzi po stronie lewej. Stan po założeniu endoprotezy w lewym stawie biodrowym.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.8</v>
       </c>
     </row>
